--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.67984706758651</v>
+        <v>7.097975148482809</v>
       </c>
       <c r="D2" t="n">
-        <v>47.16953071019694</v>
+        <v>7.665048740407004</v>
       </c>
       <c r="E2" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F2" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>85.1668209730377</v>
+        <v>13.83960840811863</v>
       </c>
       <c r="D3" t="n">
-        <v>85.02228286243</v>
+        <v>13.81612096514488</v>
       </c>
       <c r="E3" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F3" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.9081105088634</v>
+        <v>6.160067957690303</v>
       </c>
       <c r="D4" t="n">
-        <v>37.8120393098412</v>
+        <v>6.144456387849196</v>
       </c>
       <c r="E4" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F4" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43002545280195</v>
+        <v>6.894879136080317</v>
       </c>
       <c r="D5" t="n">
-        <v>42.28547306669347</v>
+        <v>6.871389373337689</v>
       </c>
       <c r="E5" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F5" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.60919297285741</v>
+        <v>3.186493858089329</v>
       </c>
       <c r="D6" t="n">
-        <v>19.54650048585927</v>
+        <v>3.176306328952131</v>
       </c>
       <c r="E6" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F6" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.06193118703188</v>
+        <v>7.972563817892681</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92116616728337</v>
+        <v>7.949689502183548</v>
       </c>
       <c r="E7" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F7" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.12160558065111</v>
+        <v>4.569760906855806</v>
       </c>
       <c r="D8" t="n">
-        <v>27.67593234525553</v>
+        <v>4.497339006104023</v>
       </c>
       <c r="E8" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F8" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.71869038286618</v>
+        <v>1.741787187215754</v>
       </c>
       <c r="D9" t="n">
-        <v>10.71585069931916</v>
+        <v>1.741325738639364</v>
       </c>
       <c r="E9" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F9" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.22095631289787</v>
+        <v>6.860905400845904</v>
       </c>
       <c r="D10" t="n">
-        <v>42.09434148700295</v>
+        <v>6.84033049163798</v>
       </c>
       <c r="E10" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F10" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.55170083565668</v>
+        <v>5.614651385794211</v>
       </c>
       <c r="D11" t="n">
-        <v>16.44688420339853</v>
+        <v>2.67261868305226</v>
       </c>
       <c r="E11" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F11" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.01980187612599</v>
+        <v>4.715717804870473</v>
       </c>
       <c r="D12" t="n">
-        <v>28.93335794193415</v>
+        <v>4.701670665564301</v>
       </c>
       <c r="E12" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F12" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.76337148729846</v>
+        <v>5.649047866686</v>
       </c>
       <c r="D13" t="n">
-        <v>34.84547281959344</v>
+        <v>5.662389333183934</v>
       </c>
       <c r="E13" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F13" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.02031423054066</v>
+        <v>6.990801062462856</v>
       </c>
       <c r="D14" t="n">
-        <v>43.06506472841899</v>
+        <v>6.998073018368085</v>
       </c>
       <c r="E14" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F14" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.75772004291623</v>
+        <v>7.273129506973888</v>
       </c>
       <c r="D15" t="n">
-        <v>44.84078673836699</v>
+        <v>7.286627844984637</v>
       </c>
       <c r="E15" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F15" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>23.12212341700116</v>
+        <v>3.757345055262688</v>
       </c>
       <c r="D16" t="n">
-        <v>32.95518842981243</v>
+        <v>5.35521811984452</v>
       </c>
       <c r="E16" t="n">
-        <v>16.31331716790925</v>
+        <v>2.650914039785254</v>
       </c>
       <c r="F16" t="n">
-        <v>16.91513220214794</v>
+        <v>2.74870898284904</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
